--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -756,7 +756,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So cùng một chỉ số và cùng đơn vị ở từng bước.</t>
+          <t>So sánh thời gian xử lý các bước: Nhận hồ sơ: 2 phút; Kiểm tra thủ công: 17 phút; Phê duyệt: 4 phút. Bước 'Kiểm tra thủ công' chiếm 17 phút là nút thắt (bottleneck) lớn nhất.</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách tác vụ ngôn ngữ biến thiên khỏi phép kiểm đã có luật hoàn chỉnh.</t>
+          <t>Tác vụ phù hợp để cân nhắc AI là các tác vụ ngôn ngữ tự nhiên hoặc mẫu phức tạp: Phân loại email tự do nhiều ý định (a), Gợi ý sản phẩm cá nhân hóa từ nhiều tín hiệu hành vi (c), và Tóm tắt phản hồi ngôn ngữ tự nhiên (e). Tính VAT (b) và kiểm tra định dạng 10 chữ số (d) là logic xác định cần dùng code thuần.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh dấu riêng từng bằng chứng: đã có hay còn thiếu.</t>
+          <t>Đánh giá mức độ sẵn sàng: Quy trình và người chịu trách nhiệm đã được ghi nhận (a), nhưng Bằng chứng đánh giá còn thiếu (b), và Mức lỗi chấp nhận được còn thiếu (c). 20 mẫu là quá ít để đại diện (d) và chưa thể triển khai ngay (e).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -628,10 +628,24 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết mỗi bước dưới dạng người thực hiện: đầu vào → hành động → đầu ra.
-Phân tích theo nguyên lý thiết kế: Viết mỗi bước dưới dạng người thực hiện: đầu vào → hành động → đầu ra.</t>
+- Lập sơ đồ quy trình hiện trạng chuẩn (1.0 điểm): Trình bày đủ 5 bước với người thực hiện, đầu vào/ra và điểm bàn giao phê duyệt.
+- Chỉ ra các điểm đáng đo thêm (1.0 điểm): Đề xuất đo thời gian tra wiki, thời gian chờ duyệt và tỷ lệ hồ sơ trên 10 triệu đồng.
+- Khẳng định chưa đủ dữ liệu nút thắt (1.0 điểm): Nêu rõ việc thiếu timestamp, thiếu thời gian hàng đợi chờ duyệt (wait time) để định vị nút thắt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quy trình hiện trạng chi tiết:
+- Bước 1: [Khách hàng] -&gt; Yêu cầu gửi qua email -&gt; [CSKH] tiếp nhận.
+- Bước 2: [CSKH] -&gt; Sao chép nội dung từ email -&gt; Công cụ: Hệ thống CRM -&gt; Đầu ra: Ticket hồ sơ trong CRM.
+- Bước 3: [CSKH / Chuyên viên] -&gt; Đọc ticket -&gt; Công cụ: Wiki nội bộ -&gt; Đầu ra: Điều khoản chính sách áp dụng.
+- Bước 4: [CSKH] -&gt; Soạn thảo câu trả lời nháp -&gt; Đầu ra: Bản nháp email phản hồi.
+- Bước 5 (Điểm bàn giao kiểm soát): Nếu giá trị hồ sơ &gt; 10 triệu đồng -&gt; [CSKH] bàn giao ticket cho [Trưởng nhóm] duyệt -&gt; [Trưởng nhóm] phê duyệt -&gt; [CSKH] gửi thư cho khách.
+2. Đánh giá định lượng nút thắt:
+- Điểm đáng đo thêm: (1) Thời gian tra cứu tài liệu trên wiki ở Bước 3; (2) Thời gian chờ Trưởng nhóm phê duyệt ở Bước 5; (3) Tỷ lệ hồ sơ có giá trị trên 10 triệu đồng so với toàn bộ yêu cầu.
+- Đã đủ dữ liệu để định lượng nút thắt chưa?: CHƯA ĐỦ DỮ LIỆU. Nhật ký mới chỉ ghi nhận trình tự các bước thực hiện, hoàn toàn chưa có dấu thời gian (timestamps) cho từng chặng, chưa có tỷ lệ lỗi hoặc số lượng yêu cầu bị ứ đọng tại hàng đợi phê duyệt của Trưởng nhóm.
+- Điều còn thiếu: Phân rã thời gian xử lý thực tế (Active Handling Time) của CSKH so với thời gian hồ sơ nằm chờ ở trạng thái nhàn rỗi (Idle Wait Time) tại Bước 5.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Lập bản đồ chuỗi giá trị (Value Stream Mapping - VSM) phân biệt giữa 'Thời gian tạo giá trị' (Touch Time: đọc wiki, soạn nháp) và 'Thời gian chờ lãng phí' (Queue/Wait Time: chờ sếp duyệt). Không thể tối ưu hóa quy trình nếu không có số liệu phân rã giữa hai loại thời gian này.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Rother, M., &amp; Shook, J. (2003). Learning to See: Value Stream Mapping. Lean Enterprise Institute (https://www.lean.org/lexicon-terms/value-stream-mapping/)</t>
         </is>
       </c>
     </row>
@@ -665,10 +679,26 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ nguyên mục tiêu, cải thiện đúng bước 18 phút và đặt điểm kiểm soát ở hồ sơ có hậu quả cao.
-Phân tích theo nguyên lý thiết kế: Giữ nguyên mục tiêu, cải thiện đúng bước 18 phút và đặt điểm kiểm soát ở hồ sơ có hậu quả cao.</t>
+- Phân định ranh giới AI, Luật và Con người chuẩn xác (1.5 điểm): Luật phân loại 8% rủi ro cao; AI RAG tra 3 wiki và soạn nháp; Con người kiểm duyệt theo phân cấp rủi ro.
+- Thiết kế đường lui khi AI lỗi (1.0 điểm): Nêu cơ chế fallback về giao diện tra cứu thủ công có gợi ý link khi AI timeout/độ tin cậy thấp.
+- Hai chỉ số đo lường trước/sau cụ thể (1.5 điểm): Nêu rõ chỉ số thời gian xử lý yêu cầu (giảm từ 25 phút xuống dưới 6 phút) và thời gian chờ duyệt của trưởng nhóm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế quy trình tương lai với ranh giới rõ ràng giữa AI, Luật tự động và Con người:
+- Phân ranh giới kỹ thuật:
++ Tự động hóa bằng API/Luật (Deterministic Rules): Tự động đồng bộ yêu cầu từ email vào CRM qua webhook/API (loại bỏ khâu chép tay thủ công); tự động phân loại ngưỡng giá trị hồ sơ (8% rủi ro cao vs 92% rủi ro thấp) dựa trên trường dữ liệu số tiền.
++ Tác nhân AI (RAG / Copilot): Tự động đọc nội dung ticket, thực hiện tìm kiếm ngữ nghĩa trên 3 trang wiki nghiệp vụ và trích xuất đúng điều khoản liên quan, sau đó soạn sẵn một bản nháp trả lời hoàn chỉnh kèm trích dẫn nguồn (giải quyết triệt để nút thắt 18 phút tra cứu).
++ Con người (Human-in-the-loop):
+  * Đối với 92% yêu cầu rủi ro thấp: CSKH chỉ cần xem nhanh bản nháp do AI soạn, chỉnh sửa nếu cần và bấm gửi (bỏ khâu Trưởng nhóm duyệt toàn bộ).
+  * Đối với 8% yêu cầu rủi ro cao: Hệ thống tự động chuyển tiếp hồ sơ và bản nháp đã chuẩn bị sẵn cho Trưởng nhóm thẩm định và phê duyệt trước khi gửi đi.
+2. Đường lui khi hệ thống AI gặp sự cố (Fallback Mechanism):
+Nếu hệ thống AI bị timeout hoặc độ tin cậy trích xuất wiki thấp (&lt; 0,7), hệ thống tự động đánh dấu cờ cảnh báo và trả về giao diện tra cứu wiki truyền thống với các đường link gợi ý để CSKH tự tra cứu thủ công mà không làm gián đoạn luồng công việc.
+3. Hai chỉ số đo lường trước / sau cải tiến:
+- Chỉ số 1 (Thời gian chu trình): Thời gian xử lý trung bình mỗi yêu cầu của CSKH (Handling Time) — Mục tiêu: Giảm từ 25 phút xuống dưới 6 phút.
+- Chỉ số 2 (Thời gian hàng đợi): Thời gian chờ phê duyệt trung bình của hồ sơ (Queue Wait Time) — Mục tiêu: Giảm 85% do giải phóng Trưởng nhóm khỏi 92% hồ sơ rủi ro thấp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tái thiết kế quy trình (Business Process Re-engineering) tập trung giải quyết đúng điểm nghẽn nặng nhất (tra wiki 18/25 phút) và chuyển đổi từ mô hình 'Kiểm soát toàn diện 100%' sang 'Kiểm soát theo rủi ro' (Risk-based Exception Approval). Kết quả là giải phóng thời gian cho quản lý và tăng năng suất cho nhân viên tuyến đầu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hammer, M. (1990). Reengineering Work: Don't Automate, Obliterate. Harvard Business Review (https://hbr.org/1990/07/reengineering-work-dont-automate-obliterate); Google Cloud AI Adoption Framework (https://cloud.google.com/ai-adoption)</t>
         </is>
       </c>
     </row>
@@ -704,10 +734,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm nơi hệ thống tự quyết, nơi làm mất hồ sơ và nơi không để lại lý do; đó là ba ranh giới cần sửa trước.
-Phân tích theo nguyên lý thiết kế: Tìm nơi hệ thống tự quyết, nơi làm mất hồ sơ và nơi không để lại lý do; đó là ba ranh giới cần sửa trước.</t>
+- Chỉ ra 3 điểm không an toàn (1.0 điểm): Nhận diện đúng việc tự loại không lưu lý do, thiếu giải trình và việc làm rơi mất hồ sơ khi lỗi.
+- Vẽ lại ranh giới Người - Máy chuẩn mực (1.0 điểm): AI chỉ trích xuất tiêu chí và giải trình; Con người giữ quyền quyết định loại bỏ cuối cùng.
+- Cơ chế đường lui dự phòng (1.0 điểm): Đưa hồ sơ vào fallback queue và xử lý thủ công an toàn khi dịch vụ AI lỗi.
+- Hai chỉ số kiểm soát rủi ro (1.0 điểm): Nêu rõ chỉ số tỷ lệ loại oan (False Rejection) và chỉ số trôi dạt phân phối/thiên kiến (Bias drift).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ba điểm không an toàn nghiêm trọng trong đề xuất ban đầu:
+- Điểm không an toàn 1: Mô hình tự động loại hồ sơ mà không lưu lý do cho điểm, vi phạm nghiêm trọng tính giải trình (Explainability) và tính tuân thủ pháp lý lao động (nguy cơ thiên kiến/phân biệt đối xử ngầm mà không kiểm toán được).
+- Điểm không an toàn 2: Mô hình tự động ra quyết định loại bỏ (Autonomous rejection without human oversight) đối với các hồ sơ &lt; 0,6 trong khi các mô hình AI sàng lọc CV có sai số và ảo giác cao.
+- Điểm không an toàn 3: Khi dịch vụ AI gặp sự cố, hồ sơ bị âm thầm bỏ khỏi hàng đợi, làm mất mát dữ liệu ứng viên và phá vỡ tính sẵn sàng của hệ thống.
+2. Vẽ lại ranh giới Người - Máy an toàn:
+- Máy móc (AI System): Đóng vai trò là công cụ trích xuất và đề xuất (Scoring &amp; Feature Extraction). Khi chấm điểm, AI bắt buộc phải tạo ra bảng phân tích tiêu chí chi tiết (ví dụ: số năm kinh nghiệm, kỹ năng khớp, chứng chỉ) kèm trích dẫn từ CV làm cơ sở giải trình. AI TUYỆT ĐỐI KHÔNG tự động loại hồ sơ.
+- Con người (HR Recruiter): Là người đưa ra quyết định từ chối hoặc mời phỏng vấn cuối cùng dựa trên bảng tóm tắt tiêu chí do AI gợi ý.
+3. Thiết kế đường lui khi dịch vụ gặp sự cố (Fallback Mechanism):
+Khi dịch vụ mô hình AI bị lỗi hoặc quá tải, toàn bộ CV ứng viên được đẩy vào hàng đợi dự phòng (Dead Letter Queue / Fallback Ingestion Queue) và chuyển sang luồng tiếp nhận truyền thống an toàn để nhân viên tuyển dụng xem xét thủ công tuần tự, bảo đảm không bao giờ làm mất bất kỳ hồ sơ nào.
+4. Hai chỉ số theo dõi rủi ro (Risk Monitoring Metrics):
+- Chỉ số 1 (Tỷ lệ sai sót loại trừ - False Rejection Rate): Tỷ lệ ứng viên tiềm năng bị mô hình chấm điểm dưới 0,6 nhưng thực tế đạt tiêu chuẩn khi chuyên viên nhân sự kiểm tra ngẫu nhiên (Audit sample).
+- Chỉ số 2 (Độ trôi và phân phối điểm - Score Distribution Drift): Theo dõi tỷ lệ hồ sơ rơi vào nhóm &lt; 0,6 theo thời gian và theo các nhóm nhân khẩu học để phát hiện sớm hiện tượng thiên kiến (Bias/Fairness drift).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tuyển dụng là lĩnh vực rủi ro cao (High-risk AI System theo EU AI Act). Mọi quyết định ảnh hưởng đến quyền lợi con người bắt buộc phải có sự giám sát của con người (Human Oversight) và giải trình được lý do (Right to Explanation). Thiết kế hệ thống AI có trách nhiệm bắt đầu từ việc bảo đảm quyền tự quyết của con người.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+EU Artificial Intelligence Act (High-Risk AI Requirements) (https://artificialintelligenceact.eu/); Barocas, S., et al. (2019). Fairness and Machine Learning (https://fairmlbook.org/)</t>
         </is>
       </c>
     </row>
@@ -788,10 +835,22 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu chỉ số, đơn vị, điểm đo và khoảng thu thập trước khi viết mục tiêu.
-Phân tích theo nguyên lý thiết kế: Nêu chỉ số, đơn vị, điểm đo và khoảng thu thập trước khi viết mục tiêu.</t>
+- Kế hoạch đo lường baseline trung thực (1.5 điểm): Nêu đủ tên chỉ số, đơn vị (phút/giờ), điểm đo (timestamp bắt đầu - kết thúc) và khoảng thu thập 30 ngày.
+- Giải thích vì sao chưa thể kết luận nút thắt (1.5 điểm): Phân tích việc chưa có dữ liệu thời gian phân đoạn và tỷ lệ lỗi khiến mọi kết luận về nút thắt chỉ là suy đoán cảm tính.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kế hoạch thiết lập Đường cơ sở – Mục tiêu – Đo lường trung thực:
+- Chỉ số đo lường chính (Metric): Thời gian chu trình xử lý yêu cầu (Resolution Lead Time).
+- Đơn vị đo: Phút (hoặc Giờ).
+- Điểm đo (Measurement Points): Bắt đầu bấm giờ ngay khi yêu cầu được ghi nhận vào hệ thống (Timestamp Tiếp nhận) và kết thúc khi câu trả lời được gửi thành công cho khách hàng (Timestamp Hoàn tất).
+- Khoảng thời gian thu thập đường cơ sở: Thu thập liên tục trên toàn bộ 2.000 yêu cầu trong vòng 30 ngày để lấy mẫu đại diện đầy đủ các ngày trong tuần và khung giờ cao điểm.
+- Phân rã dữ liệu đo: Đo riêng thời gian chờ trong hàng đợi (Wait Time) và thời gian xử lý tích cực của nhân viên (Active Touch Time), kèm phân loại theo loại yêu cầu và tỷ lệ lỗi.
+- Mục tiêu cải tiến: Chỉ thiết lập mục tiêu phần trăm (ví dụ giảm 40% thời gian xử lý P50 và P95) SAU KHI đã có số liệu baseline chính thức.
+2. Vì sao chưa thể kết luận nút thắt ở thời điểm hiện tại:
+Bởi vì hiện tại hoàn toàn chưa có số liệu đo lường thời gian phân đoạn và chưa thống kê tỷ lệ lỗi của từng khâu. Một nút thắt chỉ có thể được kết luận khi có bằng chứng định lượng chứng minh khâu đó chiếm tỷ trọng thời gian lớn nhất hoặc gây ứ đọng hàng đợi nghiêm trọng nhất. Mọi nhận định về nút thắt lúc này chỉ là phỏng đoán cảm tính.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: 'Nếu bạn không thể đo lường nó, bạn không thể cải tiến nó' (Lord Kelvin). Trong cải tiến quy trình Lean Six Sigma, giai đoạn Đo lường (Measure) phải đi trước giai đoạn Phân tích (Analyze) và Cải tiến (Improve). Thiết lập mục tiêu cải tiến khi chưa có baseline là vi phạm nguyên tắc cơ bản của khoa học quản trị.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+George, M. L. (2002). Lean Six Sigma. McGraw-Hill; Google SRE Book - Service Level Indicators (https://sre.google/sre-book/service-level-objectives/)</t>
         </is>
       </c>
     </row>
@@ -823,10 +882,21 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi đội có thể can thiệp trực tiếp vào chỉ số nào trước khi nhìn vào kết quả cuối.
-Phân tích theo nguyên lý thiết kế: Hỏi đội có thể can thiệp trực tiếp vào chỉ số nào trước khi nhìn vào kết quả cuối.</t>
+- Nêu 2 chỉ số đầu vào tác động được (1.0 điểm): Nêu đúng tính đầy đủ của dữ liệu đầu vào và độ phủ của tri thức tham chiếu.
+- Viết giả thuyết có cấu trúc nối input -&gt; output (1.0 điểm): Viết giả thuyết rõ ràng 'Nếu... thì... bởi vì...'.
+- Phép kiểm tra phân biệt độ chính xác mô hình với kết quả sản phẩm (1.0 điểm): Đưa ra phép đối chứng giữa Model Accuracy và Tỷ lệ duyệt thực tế của quy trình.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hai chỉ số đầu vào (Input Metrics) mà đội ngũ có thể tác động trực tiếp:
+- Chỉ số đầu vào 1: Tỷ lệ hồ sơ được chuẩn hóa và tự động kiểm tra tính đầy đủ của trường dữ liệu trước khi gửi (Input Data Validation Pass Rate).
+- Chỉ số đầu vào 2: Tỷ lệ tài liệu tham chiếu/chính sách được cập nhật mới nhất và gắn thẻ metadata chính xác trong kho tri thức RAG (Knowledge Base Freshness &amp; Coverage Rate).
+2. Giả thuyết nối chỉ số đầu vào với chỉ số kết quả sản phẩm:
+"NẾU chúng ta tăng tỷ lệ hồ sơ có dữ liệu đầu vào đầy đủ và chuẩn hóa lên trên 95% thông qua bộ kiểm tra biểu mẫu tự động, THÌ tỷ lệ hồ sơ được duyệt đúng ngay lần đầu (First-Time-Right Approval Rate - Output Metric) sẽ tăng tối thiểu 20%, bởi vì việc loại bỏ các thông tin thiếu sót hoặc mơ hồ từ đầu vào sẽ giúp người thẩm định không phải trả lại hồ sơ để yêu cầu bổ sung thông tin."
+3. Phép kiểm tra để tránh đồng nhất độ chính xác mô hình với kết quả sản phẩm:
+Thực hiện đo lường độc lập hai chỉ số song song: Đo Độ chính xác kỹ thuật của mô hình (Model F1-score/Accuracy trên tập test) VÀ Đo Tỷ lệ hồ sơ thực tế được duyệt thành công ngoài đời thực. Nếu mô hình đạt độ chính xác 95% nhưng tỷ lệ duyệt đúng lần đầu vẫn không tăng (ví dụ do người dùng không tin tưởng gợi ý của AI, hoặc do chính sách nội bộ bị thay đổi ngoài phạm vi mô hình), điều đó chứng minh độ chính xác kỹ thuật của mô hình không đồng nhất với giá trị thực tế của sản phẩm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Phân biệt giữa Input Metrics (những việc ta có thể trực tiếp kiểm soát/thao tác) và Output Metrics (kết quả nghiệp vụ ta mong muốn). Đồng thời, tránh 'Bẫy đo lường AI' (AI Metric Fallacy): Mô hình có độ chính xác 99% nhưng đặt vào một quy trình nghiệp vụ sai lầm thì sản phẩm vẫn thất bại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Doerr, J. (2018). Measure What Matters (https://www.whatmatters.com/); Google PAIR Guidebook - Success Metrics (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -858,10 +928,21 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết “nếu chỉ số đầu vào thay đổi thì kết quả dự kiến…” rồi nêu phép quan sát hoặc thử nghiệm.
-Phân tích theo nguyên lý thiết kế: Viết “nếu chỉ số đầu vào thay đổi thì kết quả dự kiến…” rồi nêu phép quan sát hoặc thử nghiệm.</t>
+- Chọn 2 chỉ số đầu vào hợp lý (1.0 điểm): Nêu đúng tỷ lệ trích dẫn bằng chứng và xác nhận của người dùng tại phiên đầu.
+- Viết giả thuyết kiểm chứng rõ ràng (1.0 điểm): Trình bày giả thuyết định lượng kỳ vọng giảm tỷ lệ mở lại trong khung thời gian đo lường cụ thể.
+- Thận trọng khoa học về quan hệ nhân quả (1.0 điểm): Khẳng định đây là tương quan kỳ vọng, nêu rõ các yếu tố ngoại cảnh gây nhiễu không thể khẳng định nhân quả tuyệt đối.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn hai chỉ số đầu vào (Input Metrics) hợp lý:
+- Chỉ số đầu vào 1: Tỷ lệ câu trả lời của trợ lý có đính kèm trích dẫn nguồn bằng chứng có thể kiểm chứng từ tài liệu chính thức (Evidence Grounding Rate).
+- Chỉ số đầu vào 2: Tỷ lệ người dùng xác nhận đã hiểu và hài lòng với giải pháp ngay tại phiên hỗ trợ đầu tiên (First-Contact Confirmation Rate).
+2. Giả thuyết có thể kiểm chứng (Testable Hypothesis):
+"Nếu hệ thống nâng tỷ lệ câu trả lời có trích dẫn bằng chứng cụ thể từ 60% lên trên 90%, thì tỷ lệ yêu cầu phải mở lại (Re-open Rate) được kỳ vọng sẽ giảm từ mức 18% hiện tại xuống dưới 8% trong giai đoạn thử nghiệm A/B kéo dài 4 tuần."
+3. Thận trọng về quan hệ nhân quả:
+Giả thuyết trên chỉ phát biểu một mối tương quan kỳ vọng có thể quan sát và đo lường được trong thực nghiệm. Chúng ta KHÔNG KHẲNG ĐỊNH quan hệ nhân quả tuyệt đối, bởi vì việc khách hàng mở lại yêu cầu có thể xuất phát từ nhiều nguyên nhân ngoại cảnh khác (như chất lượng dịch vụ vận chuyển bên thứ ba, sự cố kỹ thuật của sản phẩm, hoặc tâm lý người dùng) vốn nằm ngoài tầm kiểm soát của nội dung phản hồi từ AI.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tư duy khoa học thực nghiệm trong quản trị sản phẩm AI đòi hỏi người làm sản phẩm phải khiêm tốn trước dữ liệu. Việc thiết lập giả thuyết giúp định hướng hành động cải tiến, nhưng luôn phải thừa nhận các biến số gây nhiễu ngoại cảnh trước khi tuyên bố quan hệ nhân quả.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kohavi, R., et al. (2020). Trustworthy Online Controlled Experiments (https://exp-platform.com/); Harvard Business Review - A Step-by-Step Guide to Smart Business Experiments (https://hbr.org/2011/03/a-step-by-step-guide-to-smart-business-experiments)</t>
         </is>
       </c>
     </row>
@@ -944,10 +1025,20 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xem phần nào có biến thiên ngôn ngữ và phần nào có điều kiện bất biến.
-Phân tích theo nguyên lý thiết kế: Xem phần nào có biến thiên ngôn ngữ và phần nào có điều kiện bất biến.</t>
+- Phân bổ chính xác AI, Luật và Con người (2.0 điểm): Gán đúng AI cho đọc lý do tự nhiên; Luật cho so sánh số ngày; Luật/Con người cho bước chi tiền.
+- Nêu ràng buộc khiến không dùng AI (1.0 điểm): Chỉ ra ràng buộc bảo vệ dữ liệu cá nhân nhạy cảm (PII/GDPR) hoặc thiếu hạ tầng bảo mật.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân chia nhiệm vụ phù hợp giữa AI, Luật tất định và Con người:
+- Bước 1 (Đọc lý do viết tự do) -&gt; DÙNG AI (LLM): Lý do hoàn tiền của khách hàng sử dụng ngôn ngữ tự nhiên không cấu trúc, đa dạng văn phong, tiếng lóng hoặc ẩn ý. LLM phù hợp nhất để đọc hiểu ngữ nghĩa, phân loại lý do chính (sản phẩm lỗi, giao trễ, đổi ý) và trích xuất các thực thể thông tin cần thiết.
+- Bước 2 (Đối chiếu số ngày với chính sách) -&gt; DÙNG LUẬT TẤT ĐỊNH (Deterministic Business Logic / Code): Việc so sánh 'Số ngày kể từ khi nhận hàng' với ngưỡng 'Chính sách 7 ngày hoặc 30 ngày' là phép so sánh toán học và logic thời gian cứng ($Date_{request} - Date_{delivery} \le PolicyDays$). Sử dụng code Python/SQL để đảm bảo độ chính xác tuyệt đối 100%, không bao giờ dùng LLM để tính toán vì rủi ro ảo giác số học.
+- Bước 3 (Quyết định trả tiền) -&gt; PHÂN CẤP CON NGƯỜI &amp; LUẬT:
+  * Đối với các trường hợp hợp lệ thỏa mãn 100% điều kiện và số tiền nhỏ dưới hạn mức: Luật phần mềm tự động kích hoạt API hoàn tiền.
+  * Đối với các trường hợp ngoại lệ, số tiền lớn hoặc nghi ngờ gian lận: Chuyển giao diện cho Chuyên viên tài chính (Con người) xem xét và bấm nút phê duyệt cuối cùng.
+2. Một ràng buộc có thể khiến KHÔNG NÊN dùng AI ở Bước 1: Ràng buộc bảo mật dữ liệu cá nhân (GDPR/Luật Bảo vệ Dữ liệu Cá nhân), nếu lý do hoàn tiền của khách hàng chứa các thông tin nhạy cảm (như bệnh án y tế, số tài khoản ngân hàng, thông tin cá nhân) mà doanh nghiệp không có hạ tầng AI on-premises hoặc cơ chế ẩn danh hóa (masking/PII redaction) đạt chuẩn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc phân rã tác vụ (Task Allocation Principle): Giao phần ngôn ngữ tự nhiên mơ hồ cho AI xác suất, giao phần logic điều kiện và số học cho Mã nguồn tất định, và giao quyền chi tiền/phê duyệt rủi ro cho Con người và Luật kiểm soát. Không bao giờ dùng LLM làm những việc mà một câu lệnh `if-else` có thể làm tốt hơn và rẻ hơn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Task Allocation (https://pair.withgoogle.com/guidebook/); OWASP Top 10 for LLM - LLM06: Sensitive Information Disclosure.</t>
         </is>
       </c>
     </row>
@@ -1029,10 +1120,19 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh dấu phần cần dữ liệu mới, phép bảo đảm và hành động ngoài hệ thống.
-Phân tích theo nguyên lý thiết kế: Đánh dấu phần cần dữ liệu mới, phép bảo đảm và hành động ngoài hệ thống.</t>
+- Nêu đúng trách nhiệm của LLM (1.0 điểm): Hiểu ý định người dùng, trích xuất tham số và tổng hợp giải thích lịch trình.
+- Nêu đủ 3 cơ chế hỗ trợ kỹ thuật (2.0 điểm): Liệt kê chính xác API giá real-time, thuật toán tối ưu lịch tất định và cổng xác nhận của người dùng trước khi đặt vé.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Trách nhiệm cốt lõi của Mô hình ngôn ngữ lớn (LLM):
+Đóng vai trò là Bộ xử lý giao diện tự nhiên và Điều phối nhận thức (Natural Language Interface &amp; Reasoning Engine): Hiểu ý định (intent), sở thích du lịch và trích xuất các thực thể tham số (điểm đến, ngày đi, ngân sách, số lượng khách) từ câu hỏi tự do của người dùng; tổng hợp thông tin từ các công cụ hỗ trợ và giải thích lịch trình đề xuất một cách mạch lạc, thân thiện.
+2. Ba cơ chế hỗ trợ kỹ thuật bắt buộc để bảo đảm hệ thống vận hành đúng đắn:
+- Cơ chế 1: Công cụ gọi API dữ liệu thời gian thực (Real-time Tool Integration): Kết nối API bảng giá vé máy bay/khách sạn để lấy giá chính xác tại thời điểm hiện tại, vì LLM tĩnh có knowledge cutoff và không thể tự biết giá biến động theo thời gian thực.
+- Cơ chế 2: Thuật toán tối ưu hóa lịch trình tất định (Deterministic Constraint Optimization Engine): Sử dụng thuật toán quy hoạch tuyến tính hoặc mã nguồn giải quyết bài toán TSP/Lập lịch để sắp xếp thứ tự điểm tham quan theo đúng khung giờ mở/đóng cửa và khoảng cách địa lý, ngăn chặn việc LLM ảo giác về thời gian biểu.
+- Cơ chế 3: Cổng phê duyệt và xác thực của người dùng (Human-in-the-loop Confirmation Gate): Một giao diện UI hiển thị bản tóm tắt đặt vé rõ ràng và bắt buộc người dùng phải bấm nút 'Xác nhận đặt vé' trước khi gọi API thanh toán/xuất vé, tuyệt đối không để LLM tự động kích hoạt hành động tài chính không thể đảo ngược.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình kiến trúc 'LLM as Orchestrator with Deterministic Guardrails': LLM xử lý phần tương tác mềm dẻo, nhưng mọi hành động thay đổi trạng thái thế giới (State Mutation) hoặc đòi hỏi độ chính xác tuyệt đối (Toán học, Lập lịch, Thanh toán) bắt buộc phải được ủy quyền cho các dịch vụ chuyên dụng và cổng xác nhận của con người.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Documentation - Building Systems with Tools (https://docs.anthropic.com/en/docs/build-with-claude/tool-use); LangChain Tool Boundaries (https://python.langchain.com/docs/concepts/tools/)</t>
         </is>
       </c>
     </row>
@@ -1121,10 +1221,24 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi khoảng trống cần một bằng chứng cần tạo hoặc một người chịu trách nhiệm tiếp theo.
-Phân tích theo nguyên lý thiết kế: Mỗi khoảng trống cần một bằng chứng cần tạo hoặc một người chịu trách nhiệm tiếp theo.</t>
+- Xử lý khoảng trống pháp lý dữ liệu (1.0 điểm): Nêu bước rà soát ToS/PII redaction và gán trách nhiệm cho Legal/DPO.
+- Xử lý khoảng trống bộ kiểm thử (1.0 điểm): Đề xuất bổ sung edge cases/adversarial testing và gán trách nhiệm cho QA Engineer.
+- Xử lý khoảng trống trách nhiệm sự cố (1.0 điểm): Xây dựng runbook ứng phó sự cố/RACI và gán trách nhiệm cho Product Manager/Ops Lead.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Rà soát từng khoảng trống sẵn sàng và gán bước kiểm chứng cùng người chịu trách nhiệm:
+1. Khoảng trống: 500 nhật ký không rõ sự đồng ý sử dụng dữ liệu (Data Consent Gap)
+- Bước kiểm chứng: Rà soát điều khoản dịch vụ (Terms of Service) và chính sách quyền riêng tư hiện hành; thực hiện phân loại và làm sạch dữ liệu để loại bỏ thông tin định danh cá nhân (PII Redaction); nếu cần, gửi thông báo xin phép bổ sung.
+- Người chịu trách nhiệm: Chuyên viên Pháp chế / Cán bộ Bảo vệ Dữ liệu (DPO / Legal Counsel).
+2. Khoảng trống: Bộ kiểm thử chỉ có các trường hợp thuận lợi (Evaluation Bias Gap)
+- Bước kiểm chứng: Biên soạn bổ sung tối thiểu 100 trường hợp kiểm thử đối kháng (Adversarial Test Cases), các trường hợp biên (Edge Cases), dữ liệu lỗi, mơ hồ và độc hại để đánh giá tính bền bỉ của mô hình.
+- Người chịu trách nhiệm: Kỹ sư Kiểm thử Đảm bảo Chất lượng AI (AI QA / Test Engineer).
+3. Khoảng trống: Chưa có người chịu trách nhiệm khi hệ thống gặp lỗi (Accountability &amp; Operations Gap)
+- Bước kiểm chứng: Xây dựng ma trận trách nhiệm RACI và quy trình ứng phó sự cố (Incident Response Runbook); thiết lập kênh tiếp nhận lỗi khẩn cấp và phân công người trực vận hành khi hệ thống sai lệch.
+- Người chịu trách nhiệm: Quản lý Sản phẩm (Product Manager) phối hợp cùng Trưởng nhóm Vận hành Kỹ thuật (Engineering/Ops Lead).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Khung đánh giá độ sẵn sàng AI (AI Readiness Framework) đòi hỏi sự hội tụ của 4 trụ cột: Dữ liệu hợp pháp (Legal/Consent), Năng lực kỹ thuật đã kiểm chứng (Robust Evaluation), Quy trình vận hành có người chịu trách nhiệm (Accountability), và Giá trị kinh doanh đối chứng với đường cơ sở (Baseline). Thiếu bất kỳ trụ cột nào cũng tiềm ẩn rủi ro đình chỉ dự án sau này.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI Risk Management Framework (NIST AI 100-1); Google Responsible AI Practices (https://ai.google/responsibility/principles/).</t>
         </is>
       </c>
     </row>
@@ -1156,10 +1270,21 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So thứ gì cần tự kiểm soát với thứ gì có thể mua như một năng lực phổ biến.
-Phân tích theo nguyên lý thiết kế: So thứ gì cần tự kiểm soát với thứ gì có thể mua như một năng lực phổ biến.</t>
+- Chọn đúng phương án BUY ở hiện tại (1.0 điểm): Lựa chọn BUY dịch vụ API và lập luận dựa trên tính phổ thông của tác vụ, đội ngũ mỏng (2 người) và hạn 3 tuần.
+- Phân tích rõ các đánh đổi kỹ thuật (1.0 điểm): Nêu rõ ưu điểm triển khai nhanh đối trọng với rủi ro phụ thuộc vendor và tiếng Việt chuyên ngành.
+- Bằng chứng định lượng làm đảo quyết định (1.0 điểm): Đưa ra bằng chứng tỷ lệ lỗi tiếng Việt chuyên ngành cao (&gt;25%) hoặc chi phí vượt trần để chuyển sang Boost/Build.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn phương án ở thời điểm hiện tại: Chọn phương án MUA DỊCH VỤ / TẬN DỤNG CÓ SẴN (BUY / SAAS API).
+Giải thích: Tác vụ tóm tắt biên bản họp là năng lực phổ biến (commodity capability), không phải là yếu tố tạo ra lợi thế cạnh tranh cốt lõi của doanh nghiệp. Đội ngũ kỹ thuật cực kỳ mỏng (chỉ có 2 kỹ sư) và thời hạn thử nghiệm (pilot) rất gấp trong vòng 3 tuần, trong khi dữ liệu nội bộ đã được cấp phép bảo mật để sử dụng API bên ngoài. Tự xây dựng (Build) hoặc tự huấn luyện lại mô hình trong bối cảnh này là hoàn toàn bất khả thi và lãng phí nguồn lực.
+2. Đánh đổi chính (Trade-offs):
+- Ưu điểm: Tốc độ triển khai cực nhanh (có thể tích hợp trong vài ngày), chi phí đầu tư ban đầu thấp, tận dụng được năng lực của các mô hình thương mại hàng đầu.
+- Rủi ro: Phụ thuộc vào nhà cung cấp bên thứ ba (Vendor lock-in) và chất lượng xử lý tiếng Việt chuyên ngành chưa được chứng minh trên dữ liệu thực tế của công ty.
+3. Bằng chứng thực tế có thể làm ĐẢO QUYẾT ĐỊNH (chuyển sang Tinh chỉnh trên nền có sẵn - Boost/Fine-tune hoặc Tự xây):
+Nếu trong quá trình thử nghiệm pilot 3 tuần, kết quả đánh giá cho thấy nhà cung cấp tạo ra tỷ lệ lỗi/ảo giác trên 25% đối với các thuật ngữ tiếng Việt chuyên ngành đặc thù, hoặc chi phí API gọi hàng tháng vượt quá ngân sách dự kiến khi nhân rộng, đội ngũ sẽ chuyển sang phương án 'Boost' (sử dụng mô hình mã nguồn mở như Llama/Qwen kết hợp RAG hoặc LoRA fine-tuning cục bộ).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Khung quyết định Build vs Buy vs Boost (Wardley Mapping &amp; Core vs Context): Nếu tính năng thuộc vùng 'Context' (không phải cốt lõi khác biệt), nguồn lực mỏng và thời gian gấp -&gt; luôn ưu tiên BUY để kiểm chứng thị trường. Chỉ chuyển dịch sang BUILD/BOOST khi có bằng chứng định lượng về sự thất bại của giải pháp mua sẵn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Wardley, S. (2016). Wardley Maps (https://learn.wardleymaps.com/); Cagan, M. - Build vs Buy in Product Management (https://www.svpg.com/buy-vs-build/)</t>
         </is>
       </c>
     </row>
@@ -1191,10 +1316,18 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu phương án cho thời hạn trước mắt và phương án dài hạn nếu hai phương án khác nhau.
-Phân tích theo nguyên lý thiết kế: Nêu phương án cho thời hạn trước mắt và phương án dài hạn nếu hai phương án khác nhau.</t>
+- Chọn đúng phương án BOOST cục bộ (1.5 điểm): Lựa chọn tinh chỉnh mô hình mã nguồn mở cục bộ (Boost), thỏa mãn ràng buộc dữ liệu mạng riêng, năng lực ML mạnh và hạn 6 tuần.
+- Phân tích vì sao loại trừ Build và Buy (1.0 điểm): Giải thích rõ dữ liệu không được ra ngoài loại bỏ Buy SaaS; thời hạn 6 tuần loại bỏ Build from scratch.
+- Nêu bằng chứng làm đảo quyết định (0.5 điểm): Chỉ ra dữ liệu cảm biến vật lý đặc thù mà mô hình open-weights không xử lý được để chuyển sang tự xây dài hạn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn phương án ở thời điểm hiện tại: Chọn phương án ĐIỀU CHỈNH TRÊN NỀN CÓ SẴN CỤC BỘ (BOOST / ON-PREMISES OPEN-WEIGHT ADAPTATION).
+Giải thích: Chẩn đoán lỗi thiết bị là 'khác biệt cốt lõi' của sản phẩm (Core Differentiator), đòi hỏi doanh nghiệp phải nắm giữ và làm chủ tài sản trí tuệ. Đặc biệt, ràng buộc cứng về an ninh là dữ liệu tuyệt đối không được rời mạng riêng (Private Network), loại bỏ hoàn toàn khả năng sử dụng API đám mây công cộng (Buy SaaS). Đội ngũ có năng lực Machine Learning mạnh; tuy nhiên, với thời hạn bản trình diễn rất gấp (chỉ 6 tuần), việc tự xây dựng và huấn luyện mô hình nền tảng từ đầu (Build from scratch) là bất khả thi. Do đó, phương án tối ưu nhất là 'Boost': Lấy một mô hình mã nguồn mở chất lượng cao (như Llama 3, Qwen 2.5), triển khai cục bộ trong mạng riêng và tinh chỉnh (Fine-tuning qua LoRA / RAG) trên dữ liệu thiết bị của công ty.
+2. Bằng chứng có thể làm ĐẢO QUYẾT ĐỊNH (chuyển sang Tự xây hoàn toàn - Build from scratch dài hạn):
+Nếu kết quả thử nghiệm 6 tuần cho thấy các kiến trúc mô hình ngôn ngữ tổng quát có sẵn không thể giải quyết được các dạng dữ liệu cảm biến chuỗi thời gian (time-series sensor data) hoặc tín hiệu dao động vật lý đặc thù của thiết bị, và công ty huy động được ngân sách R&amp;D lớn để phát triển một kiến trúc học sâu chuyên biệt hoàn toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mô hình 'Boost' (đứng trên vai người khổng lồ) là chiến lược cân bằng hoàn hảo giữa tính bảo mật dữ liệu nội bộ (On-premises constraints), quyền sở hữu năng lực cốt lõi (Core IP) và áp lực thời gian ra mắt sản phẩm (Time-to-market). Tự xây từ đầu trong 6 tuần là ảo tưởng kỹ thuật nguy hiểm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gartner Research - Decision Framework for Generative AI (https://www.gartner.com/); NIST AI Risk Management Framework (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -1226,10 +1359,20 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi lỗi nằm ở kiến thức thay đổi hay ở cách mô hình hành xử.
-Phân tích theo nguyên lý thiết kế: Hỏi lỗi nằm ở kiến thức thay đổi hay ở cách mô hình hành xử.</t>
+- Chọn đúng RAG và giải thích thỏa đáng (1.5 điểm): Chọn RAG vì kiến thức biến động liên tục, mô hình đã chuẩn format và thiếu dataset huấn luyện.
+- Cách kiểm chứng và đánh đổi kỹ thuật (1.5 điểm): Nêu phương pháp kiểm chứng bằng tập test chính sách mới (đo Faithfulness) và phân tích đánh đổi độ trễ/hạ tầng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn kiến trúc: Chọn TRUY HỒI / CÔNG CỤ (RETRIEVAL-AUGMENTED GENERATION - RAG).
+Giải thích: Vấn đề cốt lõi của hệ thống là 'Kiến thức thay đổi động' (chính sách cập nhật liên tục), trong khi mô hình đã làm rất tốt về mặt 'Hành vi và định dạng' khi được cung cấp đúng ngữ cảnh. Hơn nữa, dự án hoàn toàn chưa có tập dữ liệu huấn luyện có nhãn được rà soát. RAG là giải pháp duy nhất cho phép cập nhật tri thức mới tức thì (Zero-day knowledge update) chỉ bằng cách cập nhật cơ sở dữ liệu vector mà không cần nạp lại trọng số mô hình.
+2. Cách kiểm chứng thực nghiệm (Validation Method):
+Xây dựng bộ benchmark gồm 30 câu hỏi về các chính sách vừa mới thay đổi; so sánh câu trả lời của mô hình khi có RAG và khi không có RAG. Đo lường chỉ số 'Độ chính xác trích dẫn' (Citation Precision) và 'Tính trung thực với ngữ cảnh' (Faithfulness Rate &gt; 95%).
+3. Đánh đổi kỹ thuật (Trade-offs):
+- Ưu điểm: Cập nhật tri thức tức thời, chi phí vận hành rẻ, loại bỏ ảo giác và có nguồn trích dẫn đối chiếu minh bạch.
+- Đánh đổi: Tăng độ trễ phản hồi (latency thêm 200-500ms cho khâu embedding/retrieval) và tăng độ phức tạp của hạ tầng đường ống dữ liệu (Vector DB, chunking pipeline).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Ma trận quyết định RAG vs Fine-tuning: 'RAG dùng để cung cấp Kiến thức (Knowledge/Facts), Fine-tuning dùng để định hình Phong cách/Hành vi (Style/Format)'. Cố gắng dùng Fine-tuning để cập nhật tri thức thường xuyên thay đổi là một phản mẫu kiến trúc (Anti-pattern) tốn kém và không hiệu quả.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Lewis, P., et al. (2020). Retrieval-Augmented Generation for Knowledge-Intensive NLP Tasks. NeurIPS 2020. https://arxiv.org/abs/2005.11401; OpenAI - RAG vs Fine-tuning Guide.</t>
         </is>
       </c>
     </row>
@@ -1261,10 +1404,20 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách “biết gì” khỏi “trả lời theo cách nào”.
-Phân tích theo nguyên lý thiết kế: Tách “biết gì” khỏi “trả lời theo cách nào”.</t>
+- Đề xuất phương án thích nghi chuẩn xác (1.5 điểm): Đề xuất Fine-tuning (SFT/LoRA) dựa trên 8.000 mẫu để sửa định dạng, duy trì RAG để lấy tài liệu pháp lý.
+- Phương pháp kiểm chứng và đánh đổi (1.5 điểm): Thiết lập tập test đo tỷ lệ tuân thủ schema và phân tích đánh đổi chi phí GPU/quản lý checkpoint.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất bước thích nghi: Kết hợp TINH CHỈNH MÔ HÌNH (SUPERVISED FINE-TUNING - SFT / LORA) TRÊN NỀN RAG HIỆN CÓ (HYBRID RAG + FINE-TUNING).
+Giải thích: Mô hình đã truy hồi đúng tài liệu pháp lý (RAG đã hoàn thành xuất sắc nhiệm vụ cung cấp kiến thức), nhưng thất bại ở khâu 'Tuân thủ định dạng báo cáo chuyên ngành' (Output Formatting &amp; Stylistic Alignment). Đội ngũ đang sở hữu tài sản vô cùng giá trị là 8.000 cặp dữ liệu đầu vào-đầu ra chuẩn mực đã được kiểm duyệt. Do đó, phương án tối ưu là sử dụng 8.000 mẫu này để fine-tune mô hình (thông qua kỹ thuật LoRA/QLoRA), dạy mô hình nắm vững cú pháp cấu trúc và văn phong báo cáo chuyên ngành.
+2. Cách kiểm chứng thực nghiệm (Validation):
+Chia 8.000 mẫu thành tập Train/Validation/Test (tỷ lệ 80/10/10). Sử dụng tập Test độc lập để đo lường tỷ lệ vượt qua bài kiểm tra cấu trúc (Schema Compliance Rate) và điểm đánh giá định dạng từ chuyên gia pháp lý (Domain Expert Rubric Score), mục tiêu đạt &gt; 98% tuân thủ định dạng.
+3. Đánh đổi kỹ thuật (Trade-offs):
+- Lợi ích: Khắc phục triệt để lỗi định dạng báo cáo, giảm độ dài prompt hướng dẫn (tiết kiệm token input) và tăng tốc độ suy luận.
+- Đánh đổi: Tốn chi phí tính toán GPU cho quá trình huấn luyện, nguy cơ suy giảm năng lực tổng quát (Catastrophic Forgetting) và phải quản lý phiên bản trọng số fine-tuned riêng biệt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tách biệt triệt để giữa 'What to know' (Nội dung tri thức -&gt; RAG đảm nhiệm) và 'How to speak' (Cách diễn đạt và định dạng chuyên ngành -&gt; Fine-tuning đảm nhiệm). Khi đã có sẵn 8.000 cặp dữ liệu vàng, Fine-tuning là giải pháp bền vững để 'đóng bánh' định dạng vào trọng số mô hình thay vì nhồi nhét prompt dài dòng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hu, E. J., et al. (2021). LoRA: Low-Rank Adaptation of Large Language Models. ICLR 2022. https://arxiv.org/abs/2106.09685; Anthropic Guide on Fine-tuning vs Prompting.</t>
         </is>
       </c>
     </row>
@@ -1299,10 +1452,21 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Gán mỗi yêu cầu cho thành phần có thể bảo đảm trực tiếp yêu cầu đó.
-Phân tích theo nguyên lý thiết kế: Gán mỗi yêu cầu cho thành phần có thể bảo đảm trực tiếp yêu cầu đó.</t>
+- Phân rã đủ 4 thành phần kiến trúc (1.5 điểm): Gán chính xác vai trò của Model, Context (sổ tay metadata), Planning (luồng kiểm tra), và Tools (IoT API, CMMS API).
+- Chỉ ra ranh giới và phụ thuộc còn thiếu (1.5 điểm): Nêu rõ cơ chế khóa phiên bản thiết bị và cổng phê duyệt của con người trước khi tạo lệnh công việc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân rã bốn thành phần kiến trúc hệ thống trợ lý bảo trì:
+- Mô hình (Model): LLM cơ sở (Foundation LLM) đóng vai trò là bộ suy luận nhận thức (Reasoning Core) để phân tích triệu chứng lỗi, diễn giải số đo cảm biến và tạo nội dung khuyến nghị.
+- Ngữ cảnh (Context / Knowledge Retrieval): Hệ thống RAG kết nối kho tài liệu sổ tay kỹ thuật (Manuals) được lập chỉ mục kèm siêu dữ liệu (Metadata) phân định chính xác số hiệu model và phiên bản thiết bị (Firmware/Hardware version).
+- Bước lập kế hoạch (Planning / Workflow Orchestrator): Đồ thị trạng thái hữu hạn (State Machine / Deterministic Workflow) quản lý tuần tự các bước kiểm tra theo quy chuẩn bảo trì kỹ thuật, kiểm soát các điều kiện tiên quyết trước khi chuyển bước.
+- Công cụ (Tools / APIs): (1) API Gateway đọc dữ liệu cảm biến thời gian thực (IoT Sensor Telemetry API); (2) API tạo phiếu công việc trên hệ thống CMMS/ERP sau khi được cấp phép.
+2. Ranh giới và phần phụ thuộc quan trọng còn thiếu:
+- Thiếu Bộ lọc đối soát phiên bản (Version Gating Boundary): Cần cơ chế tự động đọc số serial của thiết bị để khóa cứng phiên bản sổ tay tra cứu, tránh trường hợp LLM tra nhầm sổ tay đời cũ.
+- Thiếu Cổng phê duyệt của con người (Human Approval Gate): Cần giao diện xác thực chữ ký điện tử của kỹ thuật viên trước khi kích hoạt công cụ tạo lệnh công việc trên ERP, ngăn ngừa tạo lệnh rác tự động.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Một ứng dụng AI cấp công nghiệp (Enterprise AI Assistant) không bao giờ chỉ là 'LLM + Chat History'. Nó đòi hỏi kiến trúc 4 lớp vững chắc: Tầng nhận thức (Model), Tầng tri thức neo đậu (Context), Tầng điều phối trạng thái (Planning), và Tầng tương tác thế giới thực (Tools) với các chốt kiểm soát an toàn nghiêm ngặt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain StateGraph Architecture (https://python.langchain.com/docs/concepts/architecture/); Google Cloud - Industrial GenAI Assistant Design (https://cloud.google.com/architecture)</t>
         </is>
       </c>
     </row>
@@ -1337,10 +1501,21 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo luồng từ ý định đến hành động gây tác động bên ngoài và hỏi dữ liệu/quyền nằm ở đâu.
-Phân tích theo nguyên lý thiết kế: Theo luồng từ ý định đến hành động gây tác động bên ngoài và hỏi dữ liệu/quyền nằm ở đâu.</t>
+- Phân rã đủ 4 thành phần nghiệp vụ (1.5 điểm): Nêu đúng dịch vụ quản lý ngân sách, API tồn kho ERP, cổng phê duyệt và API đặt đơn.
+- Chỉ ra ranh giới ủy quyền còn thiếu (1.5 điểm): Phân tích việc LLM thiếu kiểm soát ủy quyền, nguy cơ tự đặt đơn và yêu cầu bắt buộc phải có chữ ký phê duyệt trước khi giao dịch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân rã bốn thành phần cấu trúc của trợ lý mua hàng:
+- Thành phần Ngân sách (Memory &amp; Policy State): Dịch vụ quản lý trạng thái tài chính (Financial State Service) lưu trữ ngân sách còn lại của phòng ban từ cơ sở dữ liệu kế toán, không dựa vào bộ nhớ ngữ cảnh dễ trôi của LLM.
+- Thành phần Tra cứu tồn kho (Inventory Tool): Công cụ API kết nối trực tiếp vào hệ thống quản lý kho (WMS/ERP) để kiểm tra số lượng khả dụng thời gian thực.
+- Thành phần Phê duyệt (Approval Gate / Workflow Node): Cơ chế định tuyến phê duyệt (Approval Engine) gửi thông báo kèm nút duyệt tới người có thẩm quyền qua Slack/Email khi đơn hàng vượt hạn mức quy định.
+- Thành phần Đặt hàng (Procurement Execution Tool): API giao dịch idempotent kết nối với nhà cung cấp để phát hành Purchase Order (PO).
+2. Ranh giới còn thiếu khiến quy trình chưa đáng tin cậy:
+- Thiếu Ranh giới kiểm soát giao dịch và ủy quyền (Authorization &amp; Transaction Boundary): Hiện tại LLM chỉ có lời nhắc (prompt) nên rất dễ bị Prompt Injection hoặc ảo giác tự ý gọi API đặt hàng mà không qua kiểm tra số dư ngân sách thực tế trong DB.
+- Ranh giới bất biến bắt buộc: API đặt đơn chỉ được phép cấp quyền thực thi (Execution Token) KHI VÀ CHỈ KHI có chữ ký phê duyệt hợp lệ từ cổng kiểm soát của con người.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tách biệt quyền suy luận (Reasoning Authority) khỏi quyền tài chính (Financial Authority). LLM chỉ được phép đề xuất giỏ hàng (Cart Proposal); việc khóa ngân sách và phát hành lệnh mua phải tuân thủ giao dịch ACID và cổng ủy quyền nhiều lớp của hệ thống backend doanh nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler - Patterns of Enterprise Application Architecture (https://martinfowler.com/eaaCatalog/); OWASP Top 10 for LLMs - LLM08: Excessive Agency (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
